--- a/artfynd/A 33806-2025 artfynd.xlsx
+++ b/artfynd/A 33806-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128801861</v>
       </c>
       <c r="B2" t="n">
-        <v>98626</v>
+        <v>98653</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128801800</v>
       </c>
       <c r="B3" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>128801863</v>
       </c>
       <c r="B4" t="n">
-        <v>98491</v>
+        <v>98518</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>128801815</v>
       </c>
       <c r="B5" t="n">
-        <v>98626</v>
+        <v>98653</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>128801859</v>
       </c>
       <c r="B6" t="n">
-        <v>98626</v>
+        <v>98653</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>128801864</v>
       </c>
       <c r="B7" t="n">
-        <v>98626</v>
+        <v>98653</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>128801862</v>
       </c>
       <c r="B8" t="n">
-        <v>98626</v>
+        <v>98653</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>128801857</v>
       </c>
       <c r="B9" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>128801799</v>
       </c>
       <c r="B10" t="n">
-        <v>98626</v>
+        <v>98653</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 33806-2025 artfynd.xlsx
+++ b/artfynd/A 33806-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128801861</v>
       </c>
       <c r="B2" t="n">
-        <v>98653</v>
+        <v>98659</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128801800</v>
       </c>
       <c r="B3" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>128801863</v>
       </c>
       <c r="B4" t="n">
-        <v>98518</v>
+        <v>98524</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>128801815</v>
       </c>
       <c r="B5" t="n">
-        <v>98653</v>
+        <v>98659</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>128801859</v>
       </c>
       <c r="B6" t="n">
-        <v>98653</v>
+        <v>98659</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>128801864</v>
       </c>
       <c r="B7" t="n">
-        <v>98653</v>
+        <v>98659</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>128801862</v>
       </c>
       <c r="B8" t="n">
-        <v>98653</v>
+        <v>98659</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>128801857</v>
       </c>
       <c r="B9" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>128801799</v>
       </c>
       <c r="B10" t="n">
-        <v>98653</v>
+        <v>98659</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 33806-2025 artfynd.xlsx
+++ b/artfynd/A 33806-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128801861</v>
       </c>
       <c r="B2" t="n">
-        <v>98659</v>
+        <v>98666</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128801800</v>
       </c>
       <c r="B3" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>128801863</v>
       </c>
       <c r="B4" t="n">
-        <v>98524</v>
+        <v>98531</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>128801815</v>
       </c>
       <c r="B5" t="n">
-        <v>98659</v>
+        <v>98666</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>128801859</v>
       </c>
       <c r="B6" t="n">
-        <v>98659</v>
+        <v>98666</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>128801864</v>
       </c>
       <c r="B7" t="n">
-        <v>98659</v>
+        <v>98666</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>128801862</v>
       </c>
       <c r="B8" t="n">
-        <v>98659</v>
+        <v>98666</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>128801857</v>
       </c>
       <c r="B9" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>128801799</v>
       </c>
       <c r="B10" t="n">
-        <v>98659</v>
+        <v>98666</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 33806-2025 artfynd.xlsx
+++ b/artfynd/A 33806-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128801861</v>
       </c>
       <c r="B2" t="n">
-        <v>98666</v>
+        <v>98670</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128801800</v>
       </c>
       <c r="B3" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>128801863</v>
       </c>
       <c r="B4" t="n">
-        <v>98531</v>
+        <v>98535</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>128801815</v>
       </c>
       <c r="B5" t="n">
-        <v>98666</v>
+        <v>98670</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>128801859</v>
       </c>
       <c r="B6" t="n">
-        <v>98666</v>
+        <v>98670</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>128801864</v>
       </c>
       <c r="B7" t="n">
-        <v>98666</v>
+        <v>98670</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>128801862</v>
       </c>
       <c r="B8" t="n">
-        <v>98666</v>
+        <v>98670</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>128801857</v>
       </c>
       <c r="B9" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>128801799</v>
       </c>
       <c r="B10" t="n">
-        <v>98666</v>
+        <v>98670</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 33806-2025 artfynd.xlsx
+++ b/artfynd/A 33806-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128801861</v>
       </c>
       <c r="B2" t="n">
-        <v>98670</v>
+        <v>98677</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128801800</v>
       </c>
       <c r="B3" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>128801863</v>
       </c>
       <c r="B4" t="n">
-        <v>98535</v>
+        <v>98542</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>128801815</v>
       </c>
       <c r="B5" t="n">
-        <v>98670</v>
+        <v>98677</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>128801859</v>
       </c>
       <c r="B6" t="n">
-        <v>98670</v>
+        <v>98677</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>128801864</v>
       </c>
       <c r="B7" t="n">
-        <v>98670</v>
+        <v>98677</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>128801862</v>
       </c>
       <c r="B8" t="n">
-        <v>98670</v>
+        <v>98677</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>128801857</v>
       </c>
       <c r="B9" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>128801799</v>
       </c>
       <c r="B10" t="n">
-        <v>98670</v>
+        <v>98677</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 33806-2025 artfynd.xlsx
+++ b/artfynd/A 33806-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128801861</v>
       </c>
       <c r="B2" t="n">
-        <v>98685</v>
+        <v>98690</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128801800</v>
       </c>
       <c r="B3" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>128801863</v>
       </c>
       <c r="B4" t="n">
-        <v>98550</v>
+        <v>98555</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>128801815</v>
       </c>
       <c r="B5" t="n">
-        <v>98685</v>
+        <v>98690</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>128801859</v>
       </c>
       <c r="B6" t="n">
-        <v>98685</v>
+        <v>98690</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>128801864</v>
       </c>
       <c r="B7" t="n">
-        <v>98685</v>
+        <v>98690</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>128801862</v>
       </c>
       <c r="B8" t="n">
-        <v>98685</v>
+        <v>98690</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>128801857</v>
       </c>
       <c r="B9" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>128801799</v>
       </c>
       <c r="B10" t="n">
-        <v>98685</v>
+        <v>98690</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>129092668</v>
       </c>
       <c r="B11" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 33806-2025 artfynd.xlsx
+++ b/artfynd/A 33806-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128801861</v>
       </c>
       <c r="B2" t="n">
-        <v>98690</v>
+        <v>98693</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128801800</v>
       </c>
       <c r="B3" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>128801863</v>
       </c>
       <c r="B4" t="n">
-        <v>98555</v>
+        <v>98558</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>128801815</v>
       </c>
       <c r="B5" t="n">
-        <v>98690</v>
+        <v>98693</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>128801859</v>
       </c>
       <c r="B6" t="n">
-        <v>98690</v>
+        <v>98693</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>128801864</v>
       </c>
       <c r="B7" t="n">
-        <v>98690</v>
+        <v>98693</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>128801862</v>
       </c>
       <c r="B8" t="n">
-        <v>98690</v>
+        <v>98693</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>128801857</v>
       </c>
       <c r="B9" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>128801799</v>
       </c>
       <c r="B10" t="n">
-        <v>98690</v>
+        <v>98693</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>129092668</v>
       </c>
       <c r="B11" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 33806-2025 artfynd.xlsx
+++ b/artfynd/A 33806-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128801861</v>
       </c>
       <c r="B2" t="n">
-        <v>98693</v>
+        <v>98703</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128801800</v>
       </c>
       <c r="B3" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>128801863</v>
       </c>
       <c r="B4" t="n">
-        <v>98558</v>
+        <v>98568</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>128801815</v>
       </c>
       <c r="B5" t="n">
-        <v>98693</v>
+        <v>98703</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>128801859</v>
       </c>
       <c r="B6" t="n">
-        <v>98693</v>
+        <v>98703</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>128801864</v>
       </c>
       <c r="B7" t="n">
-        <v>98693</v>
+        <v>98703</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>128801862</v>
       </c>
       <c r="B8" t="n">
-        <v>98693</v>
+        <v>98703</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>128801857</v>
       </c>
       <c r="B9" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>128801799</v>
       </c>
       <c r="B10" t="n">
-        <v>98693</v>
+        <v>98703</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>129092668</v>
       </c>
       <c r="B11" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 33806-2025 artfynd.xlsx
+++ b/artfynd/A 33806-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128801861</v>
       </c>
       <c r="B2" t="n">
-        <v>98703</v>
+        <v>98710</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128801800</v>
       </c>
       <c r="B3" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>128801863</v>
       </c>
       <c r="B4" t="n">
-        <v>98568</v>
+        <v>98575</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>128801815</v>
       </c>
       <c r="B5" t="n">
-        <v>98703</v>
+        <v>98710</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>128801859</v>
       </c>
       <c r="B6" t="n">
-        <v>98703</v>
+        <v>98710</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>128801864</v>
       </c>
       <c r="B7" t="n">
-        <v>98703</v>
+        <v>98710</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>128801862</v>
       </c>
       <c r="B8" t="n">
-        <v>98703</v>
+        <v>98710</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>128801857</v>
       </c>
       <c r="B9" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>128801799</v>
       </c>
       <c r="B10" t="n">
-        <v>98703</v>
+        <v>98710</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>129092668</v>
       </c>
       <c r="B11" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 33806-2025 artfynd.xlsx
+++ b/artfynd/A 33806-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128801861</v>
       </c>
       <c r="B2" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128801800</v>
       </c>
       <c r="B3" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>128801863</v>
       </c>
       <c r="B4" t="n">
-        <v>98575</v>
+        <v>98577</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>128801815</v>
       </c>
       <c r="B5" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>128801859</v>
       </c>
       <c r="B6" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>128801864</v>
       </c>
       <c r="B7" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>128801862</v>
       </c>
       <c r="B8" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>128801857</v>
       </c>
       <c r="B9" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>128801799</v>
       </c>
       <c r="B10" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>129092668</v>
       </c>
       <c r="B11" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 33806-2025 artfynd.xlsx
+++ b/artfynd/A 33806-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128801861</v>
       </c>
       <c r="B2" t="n">
-        <v>98712</v>
+        <v>98738</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128801800</v>
       </c>
       <c r="B3" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>128801863</v>
       </c>
       <c r="B4" t="n">
-        <v>98577</v>
+        <v>98603</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>128801815</v>
       </c>
       <c r="B5" t="n">
-        <v>98712</v>
+        <v>98738</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>128801859</v>
       </c>
       <c r="B6" t="n">
-        <v>98712</v>
+        <v>98738</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>128801864</v>
       </c>
       <c r="B7" t="n">
-        <v>98712</v>
+        <v>98738</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>128801862</v>
       </c>
       <c r="B8" t="n">
-        <v>98712</v>
+        <v>98738</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>128801857</v>
       </c>
       <c r="B9" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>128801799</v>
       </c>
       <c r="B10" t="n">
-        <v>98712</v>
+        <v>98738</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>129092668</v>
       </c>
       <c r="B11" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 33806-2025 artfynd.xlsx
+++ b/artfynd/A 33806-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128801861</v>
       </c>
       <c r="B2" t="n">
-        <v>98738</v>
+        <v>98739</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128801800</v>
       </c>
       <c r="B3" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>128801863</v>
       </c>
       <c r="B4" t="n">
-        <v>98603</v>
+        <v>98604</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>128801815</v>
       </c>
       <c r="B5" t="n">
-        <v>98738</v>
+        <v>98739</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>128801859</v>
       </c>
       <c r="B6" t="n">
-        <v>98738</v>
+        <v>98739</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>128801864</v>
       </c>
       <c r="B7" t="n">
-        <v>98738</v>
+        <v>98739</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>128801862</v>
       </c>
       <c r="B8" t="n">
-        <v>98738</v>
+        <v>98739</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>128801857</v>
       </c>
       <c r="B9" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>128801799</v>
       </c>
       <c r="B10" t="n">
-        <v>98738</v>
+        <v>98739</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>129092668</v>
       </c>
       <c r="B11" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 33806-2025 artfynd.xlsx
+++ b/artfynd/A 33806-2025 artfynd.xlsx
@@ -1601,7 +1601,7 @@
         <v>129092668</v>
       </c>
       <c r="B11" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 33806-2025 artfynd.xlsx
+++ b/artfynd/A 33806-2025 artfynd.xlsx
@@ -1601,7 +1601,7 @@
         <v>129092668</v>
       </c>
       <c r="B11" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 33806-2025 artfynd.xlsx
+++ b/artfynd/A 33806-2025 artfynd.xlsx
@@ -1601,7 +1601,7 @@
         <v>129092668</v>
       </c>
       <c r="B11" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 33806-2025 artfynd.xlsx
+++ b/artfynd/A 33806-2025 artfynd.xlsx
@@ -1601,7 +1601,7 @@
         <v>129092668</v>
       </c>
       <c r="B11" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 33806-2025 artfynd.xlsx
+++ b/artfynd/A 33806-2025 artfynd.xlsx
@@ -1601,7 +1601,7 @@
         <v>129092668</v>
       </c>
       <c r="B11" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 33806-2025 artfynd.xlsx
+++ b/artfynd/A 33806-2025 artfynd.xlsx
@@ -1601,7 +1601,7 @@
         <v>129092668</v>
       </c>
       <c r="B11" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 33806-2025 artfynd.xlsx
+++ b/artfynd/A 33806-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128801863</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128801799</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128801815</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128801859</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128801861</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128801862</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128801864</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1494,6 +1534,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128801800</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1595,6 +1640,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128801857</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1705,6 +1755,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129092668</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1806,8 +1861,26 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128801865</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>